--- a/ground_truth/motion_correction_labels_v1.xlsx
+++ b/ground_truth/motion_correction_labels_v1.xlsx
@@ -1090,14 +1090,10 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>named_tool</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>SPM12</t>
-        </is>
-      </c>
+          <t>described_only</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n"/>
       <c r="D2" s="8" t="inlineStr">
         <is>
           <t>"performed with SPM12 using Matlab 9.2 … The process comprised realigning the functional data to the mean image of each session"</t>
@@ -1145,7 +1141,11 @@
       <c r="P2" s="8" t="n"/>
       <c r="Q2" s="7" t="inlineStr">
         <is>
-          <t>co-adjudicated. Realignment identified as motion correction (SPM Realign) in consultation; four clauses adjudicated to four separate steps.</t>
+          <t>co-adjudicated. Realignment identified as motion correction (SPM Realign) in consultation; four clauses adjudicated to four separate steps.
+2026-10-22 RELABEL, method named_tool (SPM12) → described_only. Ruled by the author after seeing the motion probe v1 output; co-adjudicated — assistant located the sentence and set out the binding question, author ruled (§7).
+CALL 1 v1.5 binding test, as clarified in protocol v1.6: SPM12 is named once, for the analysis as a whole ("The fMRI data analysis was performed with SPM12 using Matlab 9.2."), and no tool is bound to the realignment, which the paper describes in its own voice. Same shape as derosa's FSL. SPM12 belongs on the inference arm, not the extraction arm; the earlier "SPM Realign" identification was an inference, not a report.
+COBIDAS §4.3 p.10 models step-level attribution ("SPM's realign tool"). That sentence is framed for papers combining tools, so the named_tool reading was defensible.
+Superseded: method_state = named_tool, method_value = SPM12.</t>
         </is>
       </c>
     </row>

--- a/ground_truth/motion_correction_labels_v1.xlsx
+++ b/ground_truth/motion_correction_labels_v1.xlsx
@@ -1621,13 +1621,13 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>described_only</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The typical pre-processing steps for the analysis of resting state data were applied, including image coregistration to correct for head motion,</t>
+          <t>FCP analysis scripts (version 1.1-beta, available at http://www.nitrc.org/frs/shownotes.php?release_id=938) (Biswal et al., 2010), which employs AFNI (Cox, 1996) and FSL (http://www.fmrib.ox.ac.uk/fsl/) (Smith et al., 2004) software packages, were used to pre-process the fMRI signals (with minor modifications, described below). The typical pre-processing steps for the analysis of resting state data were applied, including image coregistration to correct for head motion,</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1666,7 +1666,15 @@
         </is>
       </c>
       <c r="P10" s="7" t="n"/>
-      <c r="Q10" s="7" t="n"/>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 RELABEL, method described_only → deferred (target: FCP analysis scripts v1.1-beta, Biswal et al. 2010; target_kind pipeline). Rule adopted by the author on 2026-10-26 BEFORE the motion probe v3 run (prereg Amendment 7 pre-declared this relabel as pending); the edit was made after the run. Co-adjudicated — assistant located the citation sentence and proposed the rule, author ruled (§7).
+CALL 11 (protocol v1.7): the operation is named under a cited pipeline (“FCP analysis scripts … (Biswal et al., 2010) … were used to pre-process the fMRI signals … including image coregistration to correct for head motion”) and the paper states none of the four details (algorithm, transform type, reference image, cost function). Same shape as poldrack’s ref 45. AFNI and FSL are named as the packages the scripts employ, not bound to this step (CALL 1 v1.6). The EPI-to-anatomical registration (align_epi_anat.py, Saad et al. 2009) is a different D.3 row (CALL 2) and does not bear on this bullet.
+method_quote extended to include the deferring sentence (contiguous verbatim text, line breaks joined).
+Sub-items E–P left at not_reported pending the author’s ruling on whether a deferred method carries its unstated sub-items as deferred (poldrack’s pattern: deferred unless stated in-paper).
+Superseded: method_state = described_only; method_quote = the single operation sentence.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="6" t="inlineStr">

--- a/ground_truth/motion_correction_labels_v1.xlsx
+++ b/ground_truth/motion_correction_labels_v1.xlsx
@@ -1624,7 +1624,11 @@
           <t>deferred</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>FCP analysis scripts</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>FCP analysis scripts (version 1.1-beta, available at http://www.nitrc.org/frs/shownotes.php?release_id=938) (Biswal et al., 2010), which employs AFNI (Cox, 1996) and FSL (http://www.fmrib.ox.ac.uk/fsl/) (Smith et al., 2004) software packages, were used to pre-process the fMRI signals (with minor modifications, described below). The typical pre-processing steps for the analysis of resting state data were applied, including image coregistration to correct for head motion,</t>
@@ -1632,37 +1636,37 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>not_reported</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>not_reported</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>not_reported</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="J10" s="7" t="n"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>not_reported</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="L10" s="7" t="n"/>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>not_reported</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>not_reported</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="P10" s="7" t="n"/>
@@ -1672,7 +1676,8 @@
 CALL 11 (protocol v1.7): the operation is named under a cited pipeline (“FCP analysis scripts … (Biswal et al., 2010) … were used to pre-process the fMRI signals … including image coregistration to correct for head motion”) and the paper states none of the four details (algorithm, transform type, reference image, cost function). Same shape as poldrack’s ref 45. AFNI and FSL are named as the packages the scripts employ, not bound to this step (CALL 1 v1.6). The EPI-to-anatomical registration (align_epi_anat.py, Saad et al. 2009) is a different D.3 row (CALL 2) and does not bear on this bullet.
 method_quote extended to include the deferring sentence (contiguous verbatim text, line breaks joined).
 Sub-items E–P left at not_reported pending the author’s ruling on whether a deferred method carries its unstated sub-items as deferred (poldrack’s pattern: deferred unless stated in-paper).
-Superseded: method_state = described_only; method_quote = the single operation sentence.</t>
+Superseded: method_state = described_only; method_quote = the single operation sentence.
+2026-10-26, second edit (same day, after the first): method_value = FCP analysis scripts, the pipeline-name convention the other named-pipeline deferred rows carry (chen CCS; oconnor, vanderwal, weber CPAC). Sub-items E–P not_reported → deferred under CALL 7’s bullet-level default, as applied in all seven other deferred rows; none of the six is stated in-paper (no transform type, fieldmap, reference image, similarity metric, combined-interpolation statement or slice-to-volume statement; the 3 mm MNI resampling is a separate step, not a combined-transform statement). Ruled by the author; edit by the assistant. This supersedes the “pending” paragraph above. Superseded: method_value = (empty); E, G, I, K, M, O = not_reported.</t>
         </is>
       </c>
     </row>

--- a/ground_truth/motion_correction_labels_v1.xlsx
+++ b/ground_truth/motion_correction_labels_v1.xlsx
@@ -974,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -993,6 +993,7 @@
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1081,6 +1082,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>attribution</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1090,10 +1096,14 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>described_only</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="n"/>
+          <t>named_tool</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>SPM12</t>
+        </is>
+      </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
           <t>"performed with SPM12 using Matlab 9.2 … The process comprised realigning the functional data to the mean image of each session"</t>
@@ -1145,7 +1155,13 @@
 2026-10-22 RELABEL, method named_tool (SPM12) → described_only. Ruled by the author after seeing the motion probe v1 output; co-adjudicated — assistant located the sentence and set out the binding question, author ruled (§7).
 CALL 1 v1.5 binding test, as clarified in protocol v1.6: SPM12 is named once, for the analysis as a whole ("The fMRI data analysis was performed with SPM12 using Matlab 9.2."), and no tool is bound to the realignment, which the paper describes in its own voice. Same shape as derosa's FSL. SPM12 belongs on the inference arm, not the extraction arm; the earlier "SPM Realign" identification was an inference, not a report.
 COBIDAS §4.3 p.10 models step-level attribution ("SPM's realign tool"). That sentence is framed for papers combining tools, so the named_tool reading was defensible.
-Superseded: method_state = named_tool, method_value = SPM12.</t>
+Superseded: method_state = named_tool, method_value = SPM12.
+2026-10-26 (protocol v1.8, CALL 1 attribution level). RELABEL (second), method described_only → named_tool, value SPM12, attribution = package. Ruled by the author: the paper names exactly one realignment-capable package (SPM12) for the analysis as a whole, names no step-level tool, and asserts the realignment. The 2026-10-22 relabel to described_only is superseded; its reasoning (SPM12 not bound to the step) survives as the attribution level, not as a change of state. Co-adjudicated — assistant proposed the attribution level, author ruled. Superseded: method_state = described_only, method_value = (empty).</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>package</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1359,13 @@
       <c r="P5" s="7" t="n"/>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>co-adjudicated. Bullet 2 corrected to not_reported: the verbatim — '(5) co-registration of functional data to the high-resolution structural image using boundary-based registration (Greve and Fischl, 2009)' — is func→struct coregistration, a different D.3 row per CALL 2. Bullet 2 asks about non-rigid registration WITHIN the motion correction; MCFLIRT's transform type is not stated. Same correction as poldrack_2015 b2.</t>
+          <t>co-adjudicated. Bullet 2 corrected to not_reported: the verbatim — '(5) co-registration of functional data to the high-resolution structural image using boundary-based registration (Greve and Fischl, 2009)' — is func→struct coregistration, a different D.3 row per CALL 2. Bullet 2 asks about non-rigid registration WITHIN the motion correction; MCFLIRT's transform type is not stated. Same correction as poldrack_2015 b2.
+2026-10-26 (protocol v1.8, CALL 1 attribution level). attribution = step: MCFLIRT is named as the instrument of the realignment itself.</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>step</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1430,16 @@
         </is>
       </c>
       <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>co-adjudicated. 2026-10-26 (protocol v1.8, CALL 1 attribution level). attribution = package, ruled by the author; method_state and method_value unchanged (named_tool, AFNI). The paper names AFNI and FreeSurfer for its preprocessing as a whole; FreeSurfer is off the realignment-capable list, so AFNI is the single listed package; the step is asserted (“we performed … motion correction”) with no step-level tool named. The ref 23 citation does not arise: attribution (CALL 1) precedes CALL 11. Assistant located the sentences and set out the two questions, author ruled by adopting the attribution level.</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="144" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -1418,10 +1449,14 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>described_only</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n"/>
+          <t>named_tool</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>FSL</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Standard fMRI preprocessing procedures were carried out using the FSL suite (version 5.0.10) (http://fsl.fmrib.ox.ac.uk), including motion correction via ICA-AROMA (version 0.3 beta),</t>
@@ -1474,7 +1509,13 @@
 freedom linear transformation.” → FLIRT/BBR: coregistration/normalization, a different D.3 row per CALL 2.
 bullet 5 verbatim (moved from the similarity cell — not a motion bullet): “12 degrees of freedom linear transformation” → 12 DOF describes the MNI transform, not a motion cost function.
 realignment demonstrably occurred — §2.4.3 models “six motion regressors,” §2.4.9 uses mean FD — but the step producing them is never stated: a paper reporting the downstream USE of motion parameters while omitting the step itself (the CALL 3 boundary in the reverse direction).
-PROVISIONAL: §2.4.4 defers preprocessing and denoising for the FC stream to Supplemental Materials, which we do not have; §6 requires labelling from the full paper including supplement. Revisit when the supplement is obtained.</t>
+PROVISIONAL: §2.4.4 defers preprocessing and denoising for the FC stream to Supplemental Materials, which we do not have; §6 requires labelling from the full paper including supplement. Revisit when the supplement is obtained.
+2026-10-26 (protocol v1.8, CALL 1 attribution level). RELABEL, method described_only → named_tool, value FSL, attribution = package. Ruled by the author: the paper names exactly one realignment-capable package (the FSL suite; version 5.0.10 is in the quote, not in the value) for its preprocessing as a whole and asserts the motion step; ICA-AROMA is named for the step but is a structured-noise tool (CALL 4; D.3 p.57), routed off the method, so no step-level realignment tool is named. Co-adjudicated — assistant proposed the attribution level, author ruled. Superseded: method_state = described_only, method_value = (empty).</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>package</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1587,16 @@
           <t>not_reported</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="n"/>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>co-adjudicated. 2026-10-26 (protocol v1.8, CALL 1 attribution level). attribution = step, ruled by the author; method_state and method_value unchanged (named_tool, SPM8). SPM8 is named as the instrument of the realignment sentence itself (“Using SPM8 …, images were corrected for translational and rotational motion by realigning to the first image of each scanning run”); no other tool is named for the step. Assistant located the sentence, author ruled.</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="208" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -1744,7 +1794,13 @@
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>co-adjudicated. SPM's Realign &amp; Unwarp performs susceptibility-distortion correction, so 'unwarped' addresses D.3 bullet 3. JUDGMENT CALL, author-ratified.</t>
+          <t>co-adjudicated. SPM's Realign &amp; Unwarp performs susceptibility-distortion correction, so 'unwarped' addresses D.3 bullet 3. JUDGMENT CALL, author-ratified.
+2026-10-26 (protocol v1.8, CALL 1 attribution level). attribution = package, ruled by the author; method_state and method_value unchanged (named_tool, SPM12). SPM12 is named for the initial preprocessing as a whole and the realignment follows in the paper’s own voice; the earlier reading that ‘realigned and unwarped’ binds SPM’s Realign &amp; Unwarp is tool vocabulary and is not load-bearing for the method label. The Pritschet et al. (2020) citation does not arise: attribution precedes CALL 11. Assistant set out the questions, author ruled.</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>package</t>
         </is>
       </c>
     </row>
@@ -2355,13 +2411,16 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B2:B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"named_tool,described_only,deferred,absent,stated_not_performed"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E20 G2:G20 I2:I20 K2:K20 M2:M20 O2:O20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"reported,not_reported,not_applicable,deferred"</formula1>
     </dataValidation>
+    <dataValidation sqref="R2:R20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"step,package"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ground_truth/motion_correction_labels_v1.xlsx
+++ b/ground_truth/motion_correction_labels_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cwook/Documents/neurorepro/fmri-repro-agent/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7410FF3A-3A2D-CB4A-AFEC-B63EC7AC7A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1F60AA-7794-6D44-9AD6-54B7B455C844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="166">
   <si>
     <t>paper_id</t>
   </si>
@@ -2042,6 +2042,9 @@
       <c r="Q15" s="7" t="s">
         <v>85</v>
       </c>
+      <c r="R15" s="9" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="16" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
